--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_FENERBAHCE BEKO ISTANBUL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_FENERBAHCE BEKO ISTANBUL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA40"/>
+  <dimension ref="A1:BA38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>283.96</v>
+        <v>353.5600000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>283.42</v>
+        <v>353.1199999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>122.4331380989345</v>
+        <v>115.5414589941097</v>
       </c>
       <c r="E2" t="n">
-        <v>113.9651400748007</v>
+        <v>113.8423198912551</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5826923076923077</v>
+        <v>0.5481366459627329</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1462861237162646</v>
+        <v>0.1405856117898003</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4047619047619048</v>
+        <v>0.3470588235294118</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1692307692307692</v>
+        <v>0.1708074534161491</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>56</v>
+      </c>
+      <c r="N2" t="n">
+        <v>123</v>
+      </c>
+      <c r="O2" t="n">
+        <v>147</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.4565217391304348</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>36</v>
+      </c>
+      <c r="R2" t="n">
+        <v>85</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.2639751552795031</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U2" t="n">
         <v>22</v>
       </c>
-      <c r="K2" t="n">
-        <v>61</v>
-      </c>
-      <c r="L2" t="n">
-        <v>20</v>
-      </c>
-      <c r="M2" t="n">
-        <v>47</v>
-      </c>
-      <c r="N2" t="n">
-        <v>106</v>
-      </c>
-      <c r="O2" t="n">
-        <v>125</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.4807692307692308</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>31</v>
-      </c>
-      <c r="R2" t="n">
-        <v>75</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.2884615384615384</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3</v>
-      </c>
-      <c r="U2" t="n">
-        <v>17</v>
-      </c>
       <c r="V2" t="n">
-        <v>0.06538461538461539</v>
+        <v>0.06832298136645963</v>
       </c>
       <c r="W2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X2" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.06832298136645963</v>
       </c>
       <c r="Z2" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="AA2" t="n">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2807692307692308</v>
+        <v>0.3136645962732919</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.848</v>
+        <v>0.8367346938775511</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4133333333333333</v>
+        <v>0.4235294117647059</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.1764705882352941</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3698630136986301</v>
+        <v>0.3267326732673267</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.696</v>
+        <v>1.673469387755102</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.275862068965517</v>
+        <v>1.097560975609756</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.196078431372549</v>
+        <v>0.03389830508474576</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.408163265306122</v>
+        <v>1.431034482758621</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.306122448979592</v>
+        <v>5.551724137931035</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.714285714285714</v>
+        <v>6.982758620689655</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70.99000000000001</v>
+        <v>70.71200000000002</v>
       </c>
       <c r="C3" t="n">
-        <v>70.85499999999999</v>
+        <v>70.624</v>
       </c>
       <c r="D3" t="n">
-        <v>122.4331380989345</v>
+        <v>115.5414589941096</v>
       </c>
       <c r="E3" t="n">
-        <v>113.9651400748007</v>
+        <v>113.8423198912551</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5826923076923077</v>
+        <v>0.5481366459627328</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1462861237162646</v>
+        <v>0.1405856117898003</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4047619047619048</v>
+        <v>0.3470588235294118</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1692307692307692</v>
+        <v>0.1708074534161491</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>15.25</v>
+        <v>0.4</v>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>11.75</v>
+        <v>11.2</v>
       </c>
       <c r="N3" t="n">
-        <v>26.5</v>
+        <v>24.6</v>
       </c>
       <c r="O3" t="n">
-        <v>31.25</v>
+        <v>29.4</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4807692307692308</v>
+        <v>0.4565217391304347</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.75</v>
+        <v>7.2</v>
       </c>
       <c r="R3" t="n">
-        <v>18.75</v>
+        <v>17</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2884615384615384</v>
+        <v>0.2639751552795031</v>
       </c>
       <c r="T3" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="V3" t="n">
-        <v>0.06538461538461539</v>
+        <v>0.06832298136645963</v>
       </c>
       <c r="W3" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="X3" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.06832298136645963</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.25</v>
+        <v>20.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2807692307692308</v>
+        <v>0.3136645962732919</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.848</v>
+        <v>0.8367346938775511</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4133333333333333</v>
+        <v>0.4235294117647059</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.1764705882352941</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3698630136986301</v>
+        <v>0.3267326732673267</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.696</v>
+        <v>1.673469387755102</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.275862068965517</v>
+        <v>1.097560975609756</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.196078431372549</v>
+        <v>0.03389830508474576</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.408163265306122</v>
+        <v>1.431034482758621</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.306122448979592</v>
+        <v>5.551724137931036</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.714285714285714</v>
+        <v>6.982758620689656</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>282.88</v>
+        <v>352.68</v>
       </c>
       <c r="C4" t="n">
-        <v>283.42</v>
+        <v>353.1199999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>113.9651400748007</v>
+        <v>113.8423198912551</v>
       </c>
       <c r="E4" t="n">
-        <v>122.4331380989345</v>
+        <v>115.5414589941097</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5082304526748971</v>
+        <v>0.5198675496688742</v>
       </c>
       <c r="G4" t="n">
-        <v>0.132578040255514</v>
+        <v>0.1296858177547225</v>
       </c>
       <c r="H4" t="n">
-        <v>0.355072463768116</v>
+        <v>0.327485380116959</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3127572016460906</v>
+        <v>0.2913907284768212</v>
       </c>
       <c r="J4" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
+        <v>45</v>
+      </c>
+      <c r="N4" t="n">
+        <v>152</v>
+      </c>
+      <c r="O4" t="n">
+        <v>180</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.5960264900662252</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>22</v>
+      </c>
+      <c r="R4" t="n">
+        <v>57</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1887417218543046</v>
+      </c>
+      <c r="T4" t="n">
+        <v>8</v>
+      </c>
+      <c r="U4" t="n">
+        <v>20</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.06622516556291391</v>
+      </c>
+      <c r="W4" t="n">
+        <v>5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.05298013245033113</v>
+      </c>
+      <c r="Z4" t="n">
         <v>37</v>
       </c>
-      <c r="N4" t="n">
-        <v>130</v>
-      </c>
-      <c r="O4" t="n">
-        <v>155</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.6378600823045267</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>20</v>
-      </c>
-      <c r="R4" t="n">
-        <v>45</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.1851851851851852</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>13</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.05349794238683128</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.04938271604938271</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>28</v>
-      </c>
       <c r="AA4" t="n">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3868312757201646</v>
+        <v>0.3874172185430463</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.3859649122807017</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.4</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.2978723404255319</v>
+        <v>0.3162393162393162</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.67741935483871</v>
+        <v>1.688888888888889</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.8</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.8773584905660378</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8163265306122449</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.8979591836734694</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.727272727272727</v>
+        <v>1.735849056603774</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.522727272727272</v>
+        <v>5.69811320754717</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.25</v>
+        <v>7.433962264150943</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70.72</v>
+        <v>70.536</v>
       </c>
       <c r="C5" t="n">
-        <v>70.85499999999999</v>
+        <v>70.624</v>
       </c>
       <c r="D5" t="n">
-        <v>113.9651400748007</v>
+        <v>113.8423198912551</v>
       </c>
       <c r="E5" t="n">
-        <v>122.4331380989345</v>
+        <v>115.5414589941096</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5082304526748971</v>
+        <v>0.5198675496688743</v>
       </c>
       <c r="G5" t="n">
-        <v>0.132578040255514</v>
+        <v>0.1296858177547225</v>
       </c>
       <c r="H5" t="n">
-        <v>0.355072463768116</v>
+        <v>0.327485380116959</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3127572016460906</v>
+        <v>0.2913907284768212</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M5" t="n">
         <v>9</v>
       </c>
-      <c r="M5" t="n">
-        <v>9.25</v>
-      </c>
       <c r="N5" t="n">
-        <v>32.5</v>
+        <v>30.4</v>
       </c>
       <c r="O5" t="n">
-        <v>38.75</v>
+        <v>36</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6378600823045267</v>
+        <v>0.5960264900662252</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="R5" t="n">
-        <v>11.25</v>
+        <v>11.4</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1851851851851852</v>
+        <v>0.1887417218543047</v>
       </c>
       <c r="T5" t="n">
-        <v>0.75</v>
+        <v>1.6</v>
       </c>
       <c r="U5" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="V5" t="n">
-        <v>0.05349794238683128</v>
+        <v>0.06622516556291391</v>
       </c>
       <c r="W5" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.04938271604938271</v>
+        <v>0.05298013245033113</v>
       </c>
       <c r="Z5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3868312757201646</v>
+        <v>0.3874172185430463</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.3859649122807018</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.4</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.2978723404255319</v>
+        <v>0.3162393162393163</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.67741935483871</v>
+        <v>1.688888888888889</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.8773584905660378</v>
+        <v>0.9473684210526317</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8163265306122449</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.8979591836734694</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.727272727272727</v>
+        <v>1.735849056603773</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.522727272727272</v>
+        <v>5.69811320754717</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.25</v>
+        <v>7.433962264150943</v>
       </c>
     </row>
     <row r="7">
@@ -1429,40 +1429,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F8" t="n">
         <v>7</v>
       </c>
       <c r="G8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K8" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
         <v>5</v>
@@ -1471,58 +1471,58 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>7</v>
+      </c>
+      <c r="R8" t="n">
         <v>6</v>
       </c>
-      <c r="Q8" t="n">
-        <v>6</v>
-      </c>
-      <c r="R8" t="n">
-        <v>3</v>
-      </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T8" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="U8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.857</v>
+        <v>0.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AC8" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.419</v>
+        <v>0.429</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AH8" t="n">
         <v>2</v>
@@ -1537,54 +1537,54 @@
         <v>5</v>
       </c>
       <c r="AL8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.417</v>
+        <v>0.333</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>237:56</t>
+          <t>143:26</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>61.88</v>
+        <v>74.64</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.518</v>
+        <v>0.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.519</v>
+        <v>0.503</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.911</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.097</v>
+        <v>0.094</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.018</v>
+        <v>0.046</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.5</v>
+        <v>3.857</v>
       </c>
       <c r="AV8" t="n">
-        <v>9.167</v>
+        <v>9.286</v>
       </c>
       <c r="AW8" t="n">
-        <v>12.667</v>
+        <v>13.143</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.128</v>
+        <v>0.259</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.011</v>
+        <v>0.025</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.065</v>
+        <v>0.142</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.194</v>
+        <v>0.216</v>
       </c>
     </row>
     <row r="9">
@@ -1594,22 +1594,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H9" t="n">
         <v>7</v>
@@ -1618,16 +1618,16 @@
         <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L9" t="n">
         <v>8</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
         <v>5</v>
@@ -1636,25 +1636,25 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S9" t="n">
         <v>16</v>
       </c>
       <c r="T9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1663,13 +1663,13 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Z9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.944</v>
       </c>
       <c r="AB9" t="n">
         <v>2</v>
@@ -1684,72 +1684,72 @@
         <v>1</v>
       </c>
       <c r="AF9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI9" t="n">
         <v>3</v>
       </c>
-      <c r="AG9" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="AK9" t="n">
         <v>4</v>
       </c>
       <c r="AL9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.4</v>
+        <v>0.308</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>259:14</t>
+          <t>146:37</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>39.4</v>
+        <v>49.4</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.617</v>
+        <v>0.579</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.64</v>
+        <v>0.601</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.117</v>
+        <v>1.032</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.127</v>
+        <v>0.142</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.233</v>
+        <v>0.184</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.6</v>
+        <v>0.714</v>
       </c>
       <c r="AV9" t="n">
-        <v>6</v>
+        <v>5.429</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.6</v>
+        <v>6.143</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.075</v>
+        <v>0.167</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.04</v>
+        <v>0.066</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.155</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.026</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="10">
@@ -1759,91 +1759,91 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="D10" t="n">
+        <v>24</v>
+      </c>
+      <c r="E10" t="n">
+        <v>42</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>19</v>
+      </c>
+      <c r="H10" t="n">
+        <v>15</v>
+      </c>
+      <c r="I10" t="n">
         <v>21</v>
       </c>
-      <c r="E10" t="n">
-        <v>38</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="J10" t="n">
+        <v>18</v>
+      </c>
+      <c r="K10" t="n">
+        <v>13</v>
+      </c>
+      <c r="L10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R10" t="n">
         <v>12</v>
       </c>
-      <c r="H10" t="n">
-        <v>8</v>
-      </c>
-      <c r="I10" t="n">
-        <v>13</v>
-      </c>
-      <c r="J10" t="n">
-        <v>15</v>
-      </c>
-      <c r="K10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L10" t="n">
-        <v>6</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4</v>
-      </c>
-      <c r="R10" t="n">
-        <v>11</v>
-      </c>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="T10" t="n">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="U10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="Z10" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.765</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AB10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AC10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.333</v>
+        <v>0.417</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1858,63 +1858,63 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
         <v>2</v>
       </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1</v>
-      </c>
       <c r="AL10" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.1</v>
+        <v>0.125</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>190:15</t>
+          <t>125:50</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>59.72</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.45</v>
+        <v>0.443</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.476</v>
+        <v>0.491</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.887</v>
+        <v>0.917</v>
       </c>
       <c r="AS10" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="AY10" t="n">
         <v>0.067</v>
       </c>
-      <c r="AT10" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>16.25</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0.041</v>
-      </c>
       <c r="AZ10" t="n">
-        <v>0.044</v>
+        <v>0.124</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.135</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="11">
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>33:24</t>
+          <t>03:23</t>
         </is>
       </c>
       <c r="AO11" t="n">
@@ -2089,22 +2089,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D12" t="n">
         <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H12" t="n">
         <v>3</v>
@@ -2113,10 +2113,10 @@
         <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2137,25 +2137,25 @@
         <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T12" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>7</v>
@@ -2170,10 +2170,10 @@
         <v>2</v>
       </c>
       <c r="AC12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2188,63 +2188,63 @@
         <v>1</v>
       </c>
       <c r="AI12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AK12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AL12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.364</v>
+        <v>0.462</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>96:05</t>
+          <t>74:34</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>26.32</v>
+        <v>30.32</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.643</v>
+        <v>0.66</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.672</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.14</v>
+        <v>1.187</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.152</v>
+        <v>0.132</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.143</v>
+        <v>0.12</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="AW12" t="n">
-        <v>8</v>
+        <v>9.25</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.135</v>
+        <v>0.202</v>
       </c>
       <c r="AY12" t="n">
         <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.062</v>
+        <v>0.096</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -2254,40 +2254,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G13" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
         <v>2</v>
@@ -2296,120 +2296,120 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>9</v>
+      </c>
+      <c r="R13" t="n">
+        <v>10</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>63</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC13" t="n">
         <v>8</v>
       </c>
-      <c r="Q13" t="n">
-        <v>8</v>
-      </c>
-      <c r="R13" t="n">
-        <v>8</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>45</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2</v>
-      </c>
-      <c r="V13" t="n">
-        <v>8</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>7</v>
-      </c>
       <c r="AD13" t="n">
-        <v>0.714</v>
+        <v>0.75</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AH13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="AK13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AL13" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.476</v>
+        <v>0.464</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>240:00</t>
+          <t>139:48</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>49</v>
+        <v>62.44</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.756</v>
+        <v>0.736</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.756</v>
+        <v>0.739</v>
       </c>
       <c r="AR13" t="n">
         <v>1.265</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.163</v>
+        <v>0.144</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.75</v>
+        <v>0.778</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.125</v>
+        <v>5.889</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.875</v>
+        <v>6.667</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.101</v>
+        <v>0.222</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.011</v>
+        <v>0.043</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.055</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="14">
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="AO14" t="n">
@@ -2584,7 +2584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
         <v>17</v>
@@ -2593,13 +2593,13 @@
         <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H15" t="n">
         <v>6</v>
@@ -2608,7 +2608,7 @@
         <v>6</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
         <v>9</v>
@@ -2620,7 +2620,7 @@
         <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2632,19 +2632,19 @@
         <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S15" t="n">
         <v>6</v>
       </c>
       <c r="T15" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -2665,10 +2665,10 @@
         <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2683,63 +2683,63 @@
         <v>1</v>
       </c>
       <c r="AI15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AM15" t="n">
         <v>0</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>96:33</t>
+          <t>79:27</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>16.64</v>
+        <v>22.64</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.55</v>
+        <v>0.344</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.672</v>
+        <v>0.456</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.022</v>
+        <v>0.751</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.24</v>
+        <v>0.177</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.6</v>
+        <v>0.375</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.142</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.068</v>
+        <v>0.076</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.111</v>
+        <v>0.136</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.008</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="16">
@@ -2749,7 +2749,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
         <v>26</v>
@@ -2758,13 +2758,13 @@
         <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F16" t="n">
         <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H16" t="n">
         <v>5</v>
@@ -2776,10 +2776,10 @@
         <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M16" t="n">
         <v>1</v>
@@ -2791,25 +2791,25 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="U16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -2821,10 +2821,10 @@
         <v>10</v>
       </c>
       <c r="Z16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.769</v>
+        <v>0.714</v>
       </c>
       <c r="AB16" t="n">
         <v>1</v>
@@ -2839,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -2857,54 +2857,54 @@
         <v>3</v>
       </c>
       <c r="AL16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.429</v>
+        <v>0.3</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>190:47</t>
+          <t>129:10</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>31.2</v>
+        <v>38.2</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.5</v>
+        <v>0.404</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.461</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.833</v>
+        <v>0.681</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.256</v>
+        <v>0.262</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.238</v>
+        <v>0.192</v>
       </c>
       <c r="AU16" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.625</v>
+        <v>2.6</v>
       </c>
       <c r="AW16" t="n">
-        <v>3.625</v>
+        <v>3.4</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.081</v>
+        <v>0.147</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.021</v>
+        <v>0.037</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.044</v>
+        <v>0.074</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.065</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="17">
@@ -2914,16 +2914,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -2944,7 +2944,7 @@
         <v>2</v>
       </c>
       <c r="L17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
@@ -2956,25 +2956,25 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
         <v>6</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -2983,13 +2983,13 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AA17" t="n">
-        <v>1</v>
+        <v>0.846</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -3029,47 +3029,47 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>25:23</t>
+          <t>33:25</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>13.76</v>
+        <v>17.76</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.667</v>
+        <v>0.583</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.743</v>
+        <v>0.654</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.163</v>
+        <v>1.014</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.218</v>
+        <v>0.225</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.444</v>
+        <v>0.333</v>
       </c>
       <c r="AU17" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AV17" t="n">
         <v>3</v>
       </c>
       <c r="AW17" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.267</v>
+        <v>0.264</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.258</v>
+        <v>0.217</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.094</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.024</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="18">
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
         <v>11</v>
@@ -3094,7 +3094,7 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
         <v>4</v>
@@ -3106,7 +3106,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L18" t="n">
         <v>3</v>
@@ -3127,25 +3127,25 @@
         <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>4</v>
@@ -3187,51 +3187,51 @@
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM18" t="n">
         <v>0</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>99:55</t>
+          <t>45:26</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>11.64</v>
+        <v>12.64</v>
       </c>
       <c r="AP18" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="AT18" t="n">
         <v>0.5</v>
       </c>
-      <c r="AQ18" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0.172</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0.571</v>
-      </c>
       <c r="AU18" t="n">
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AW18" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.057</v>
+        <v>0.138</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.039</v>
+        <v>0.08</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.06</v>
+        <v>0.158</v>
       </c>
       <c r="BA18" t="n">
         <v>0</v>
@@ -3244,82 +3244,82 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D19" t="n">
+        <v>13</v>
+      </c>
+      <c r="E19" t="n">
+        <v>18</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>7</v>
+      </c>
+      <c r="I19" t="n">
         <v>12</v>
-      </c>
-      <c r="E19" t="n">
-        <v>16</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>6</v>
-      </c>
-      <c r="I19" t="n">
-        <v>10</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
       </c>
       <c r="K19" t="n">
+        <v>16</v>
+      </c>
+      <c r="L19" t="n">
         <v>13</v>
       </c>
-      <c r="L19" t="n">
-        <v>12</v>
-      </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
+        <v>5</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>3</v>
-      </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T19" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Z19" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.889</v>
+        <v>0.857</v>
       </c>
       <c r="AB19" t="n">
         <v>1</v>
@@ -3359,47 +3359,47 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>180:33</t>
+          <t>103:49</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>23.4</v>
+        <v>27.28</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.75</v>
+        <v>0.722</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.735</v>
+        <v>0.709</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.282</v>
+        <v>1.21</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.128</v>
+        <v>0.147</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.375</v>
+        <v>0.389</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AV19" t="n">
-        <v>5.333</v>
+        <v>4.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.667</v>
+        <v>4.75</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.064</v>
+        <v>0.131</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.151</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.185</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="20">
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -3436,7 +3436,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L20" t="n">
         <v>5</v>
@@ -3570,163 +3570,163 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>408</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="T21" t="n">
+        <v>468</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>123</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>147</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>85</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="AH21" t="n">
         <v>12</v>
       </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>0.545</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>0.327</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>1025:00</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>2</v>
+        <v>412.56</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>0.548</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>0.575</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>0.989</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>0.141</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>0.171</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>1.431</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>5.552</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>6.983</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="BA21" t="n">
         <v>0</v>
@@ -3735,163 +3735,163 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>402</v>
+      </c>
+      <c r="D22" t="n">
+        <v>94</v>
+      </c>
+      <c r="E22" t="n">
+        <v>169</v>
+      </c>
+      <c r="F22" t="n">
+        <v>42</v>
+      </c>
+      <c r="G22" t="n">
+        <v>133</v>
+      </c>
+      <c r="H22" t="n">
+        <v>88</v>
+      </c>
+      <c r="I22" t="n">
+        <v>122</v>
+      </c>
+      <c r="J22" t="n">
+        <v>92</v>
+      </c>
+      <c r="K22" t="n">
+        <v>111</v>
+      </c>
+      <c r="L22" t="n">
+        <v>56</v>
+      </c>
+      <c r="M22" t="n">
+        <v>26</v>
+      </c>
+      <c r="N22" t="n">
+        <v>29</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>45</v>
+      </c>
+      <c r="R22" t="n">
+        <v>90</v>
+      </c>
+      <c r="S22" t="n">
+        <v>110</v>
+      </c>
+      <c r="T22" t="n">
+        <v>483</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
         <v>4</v>
       </c>
-      <c r="C22" t="n">
-        <v>347</v>
-      </c>
-      <c r="D22" t="n">
-        <v>96</v>
-      </c>
-      <c r="E22" t="n">
-        <v>173</v>
-      </c>
-      <c r="F22" t="n">
+      <c r="X22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>152</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>180</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>57</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AK22" t="n">
         <v>37</v>
       </c>
-      <c r="G22" t="n">
-        <v>87</v>
-      </c>
-      <c r="H22" t="n">
-        <v>44</v>
-      </c>
-      <c r="I22" t="n">
-        <v>59</v>
-      </c>
-      <c r="J22" t="n">
-        <v>69</v>
-      </c>
-      <c r="K22" t="n">
-        <v>89</v>
-      </c>
-      <c r="L22" t="n">
-        <v>51</v>
-      </c>
-      <c r="M22" t="n">
-        <v>14</v>
-      </c>
-      <c r="N22" t="n">
-        <v>26</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>47</v>
-      </c>
-      <c r="R22" t="n">
-        <v>81</v>
-      </c>
-      <c r="S22" t="n">
-        <v>80</v>
-      </c>
-      <c r="T22" t="n">
-        <v>404</v>
-      </c>
-      <c r="U22" t="n">
-        <v>22</v>
-      </c>
-      <c r="V22" t="n">
-        <v>61</v>
-      </c>
-      <c r="W22" t="n">
-        <v>20</v>
-      </c>
-      <c r="X22" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>106</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>125</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0.848</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>31</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>75</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0.413</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0.176</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>27</v>
-      </c>
       <c r="AL22" t="n">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.37</v>
+        <v>0.316</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>825:00</t>
+          <t>1025:00</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>334.96</v>
+        <v>408.68</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.583</v>
+        <v>0.52</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.607</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.036</v>
+        <v>0.984</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.146</v>
+        <v>0.13</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.169</v>
+        <v>0.291</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.408</v>
+        <v>1.736</v>
       </c>
       <c r="AV22" t="n">
-        <v>5.306</v>
+        <v>5.698</v>
       </c>
       <c r="AW22" t="n">
-        <v>6.714</v>
+        <v>7.434</v>
       </c>
       <c r="AX22" t="n">
         <v>0.2</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.081</v>
+        <v>0.065</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.129</v>
+        <v>0.131</v>
       </c>
       <c r="BA22" t="n">
         <v>0</v>
@@ -3900,460 +3900,460 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>4</v>
-      </c>
-      <c r="C23" t="n">
-        <v>323</v>
-      </c>
-      <c r="D23" t="n">
-        <v>77</v>
-      </c>
-      <c r="E23" t="n">
-        <v>137</v>
-      </c>
-      <c r="F23" t="n">
-        <v>31</v>
-      </c>
-      <c r="G23" t="n">
-        <v>106</v>
-      </c>
-      <c r="H23" t="n">
-        <v>76</v>
-      </c>
-      <c r="I23" t="n">
-        <v>102</v>
-      </c>
-      <c r="J23" t="n">
-        <v>76</v>
-      </c>
-      <c r="K23" t="n">
-        <v>75</v>
-      </c>
-      <c r="L23" t="n">
-        <v>49</v>
-      </c>
-      <c r="M23" t="n">
-        <v>23</v>
-      </c>
-      <c r="N23" t="n">
-        <v>26</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>37</v>
-      </c>
-      <c r="R23" t="n">
-        <v>72</v>
-      </c>
-      <c r="S23" t="n">
-        <v>89</v>
-      </c>
-      <c r="T23" t="n">
-        <v>384</v>
-      </c>
-      <c r="U23" t="n">
-        <v>40</v>
-      </c>
-      <c r="V23" t="n">
-        <v>44</v>
-      </c>
-      <c r="W23" t="n">
-        <v>36</v>
-      </c>
-      <c r="X23" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>130</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>155</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0.839</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>45</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>94</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>0.298</v>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>825:00</t>
-        </is>
-      </c>
-      <c r="AO23" t="n">
-        <v>331.88</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0.508</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0.5610000000000001</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0.973</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0.313</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>1.727</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>5.523</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr"/>
+      <c r="BA23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="inlineStr"/>
-      <c r="AO24" t="inlineStr"/>
-      <c r="AP24" t="inlineStr"/>
-      <c r="AQ24" t="inlineStr"/>
-      <c r="AR24" t="inlineStr"/>
-      <c r="AS24" t="inlineStr"/>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AU24" t="inlineStr"/>
-      <c r="AV24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr"/>
-      <c r="AX24" t="inlineStr"/>
-      <c r="AY24" t="inlineStr"/>
-      <c r="AZ24" t="inlineStr"/>
-      <c r="BA24" t="inlineStr"/>
+          <t>#2 W. BALDWIN IV (Per Game)</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>87</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>28:41</t>
+        </is>
+      </c>
+      <c r="AO24" t="n">
+        <v>14.928</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.857</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>9.286</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>13.143</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0.216</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>#2 W. BALDWIN IV (Per Game)</t>
+          <t>#4 N. MELLI (Per Game)</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" t="n">
-        <v>14.5</v>
+        <v>10.2</v>
       </c>
       <c r="D25" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="E25" t="n">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="F25" t="n">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="G25" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="H25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>65</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AG25" t="n">
         <v>0.25</v>
       </c>
-      <c r="I25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J25" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T25" t="n">
-        <v>73</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0.857</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0.419</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
       <c r="AH25" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AJ25" t="n">
         <v>0.667</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.25</v>
+        <v>0.8</v>
       </c>
       <c r="AL25" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.417</v>
+        <v>0.308</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>59:29</t>
+          <t>29:19</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>15.47</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.518</v>
+        <v>0.579</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.519</v>
+        <v>0.601</v>
       </c>
       <c r="AR25" t="n">
-        <v>0.9370000000000001</v>
+        <v>1.032</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.097</v>
+        <v>0.142</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.018</v>
+        <v>0.184</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.5</v>
+        <v>0.714</v>
       </c>
       <c r="AV25" t="n">
-        <v>9.167</v>
+        <v>5.429</v>
       </c>
       <c r="AW25" t="n">
-        <v>12.667</v>
+        <v>6.143</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.128</v>
+        <v>0.167</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.011</v>
+        <v>0.066</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.065</v>
+        <v>0.155</v>
       </c>
       <c r="BA25" t="n">
-        <v>0.194</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>#4 N. MELLI (Per Game)</t>
+          <t>#8 T. HORTON TUCKER (Per Game)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>11</v>
+        <v>13.8</v>
       </c>
       <c r="D26" t="n">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="E26" t="n">
-        <v>4.75</v>
+        <v>8.4</v>
       </c>
       <c r="F26" t="n">
-        <v>1.25</v>
+        <v>0.4</v>
       </c>
       <c r="G26" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="H26" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="J26" t="n">
-        <v>0.75</v>
+        <v>3.6</v>
       </c>
       <c r="K26" t="n">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="M26" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.25</v>
+        <v>0.4</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="U26" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -4362,193 +4362,193 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.75</v>
+        <v>6.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.286</v>
+        <v>0.417</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.4</v>
+        <v>0.125</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>64:48</t>
+          <t>25:10</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>9.85</v>
+        <v>15.048</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.617</v>
+        <v>0.443</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.64</v>
+        <v>0.491</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.117</v>
+        <v>0.917</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.127</v>
+        <v>0.066</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.233</v>
+        <v>0.246</v>
       </c>
       <c r="AU26" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>6</v>
+        <v>12.2</v>
       </c>
       <c r="AW26" t="n">
-        <v>6.6</v>
+        <v>15.8</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.075</v>
+        <v>0.297</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.04</v>
+        <v>0.067</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.124</v>
       </c>
       <c r="BA26" t="n">
-        <v>0.026</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>#8 T. HORTON TUCKER (Per Game)</t>
+          <t>#11 B. BOSTON JR. (Per Game)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>13.25</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.75</v>
+        <v>0.4</v>
       </c>
       <c r="S27" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>47</v>
+        <v>-1</v>
       </c>
       <c r="U27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.765</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -4557,106 +4557,106 @@
         <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>47:33</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>14.93</v>
+        <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.476</v>
+        <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.887</v>
+        <v>0</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.067</v>
+        <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>16.25</v>
+        <v>0</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.155</v>
+        <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.041</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.044</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
-        <v>0.135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>#11 B. BOSTON JR. (Per Game)</t>
+          <t>#12 N. DE COLO (Per Game)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -4665,310 +4665,310 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="R28" t="n">
+        <v>2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T28" t="n">
+        <v>38</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AD28" t="n">
         <v>0.5</v>
       </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
       <c r="AE28" t="n">
         <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>0.462</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>6.064</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.187</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>0.132</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>0.202</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>0.096</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>#12 N. DE COLO (Per Game)</t>
+          <t>#13 T. BIBEROVIC (Per Game)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>7.5</v>
+        <v>15.8</v>
       </c>
       <c r="D29" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="E29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R29" t="n">
         <v>2</v>
       </c>
-      <c r="F29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="G29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="H29" t="n">
+      <c r="S29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T29" t="n">
+        <v>63</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD29" t="n">
         <v>0.75</v>
       </c>
-      <c r="I29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
+      <c r="AE29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1</v>
       </c>
-      <c r="Q29" t="n">
-        <v>1</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T29" t="n">
-        <v>33</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0.25</v>
-      </c>
       <c r="AI29" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.5</v>
+        <v>0.833</v>
       </c>
       <c r="AK29" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.75</v>
+        <v>5.6</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.364</v>
+        <v>0.464</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>24:01</t>
+          <t>27:57</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>6.58</v>
+        <v>12.488</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.643</v>
+        <v>0.736</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.672</v>
+        <v>0.739</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.14</v>
+        <v>1.265</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.152</v>
+        <v>0.144</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.143</v>
+        <v>0.019</v>
       </c>
       <c r="AU29" t="n">
-        <v>2.75</v>
+        <v>0.778</v>
       </c>
       <c r="AV29" t="n">
-        <v>5.25</v>
+        <v>5.889</v>
       </c>
       <c r="AW29" t="n">
-        <v>8</v>
+        <v>6.667</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.135</v>
+        <v>0.222</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>0.043</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.062</v>
+        <v>0.06</v>
       </c>
       <c r="BA29" t="n">
-        <v>0.09</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>#13 T. BIBEROVIC (Per Game)</t>
+          <t>#17 O. BITIM (Per Game)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -4977,43 +4977,43 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
@@ -5022,328 +5022,328 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.714</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.476</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>60:00</t>
+          <t>00:01</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>12.25</v>
+        <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.756</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.756</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.265</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.163</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>5.125</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>5.875</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.101</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#17 O. BITIM (Per Game)</t>
+          <t>#18 M. JANTUNEN (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>21</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AO31" t="n">
+        <v>4.528</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AV31" t="n">
         <v>4</v>
       </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>0</v>
-      </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>0.142</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>0.076</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#18 M. JANTUNEN (Per Game)</t>
+          <t>#20 D. HALL (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>4.25</v>
+        <v>5.2</v>
       </c>
       <c r="D32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
         <v>1</v>
       </c>
-      <c r="E32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1.5</v>
-      </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>0.25</v>
+        <v>1.6</v>
       </c>
       <c r="K32" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="L32" t="n">
-        <v>1.25</v>
+        <v>0.8</v>
       </c>
       <c r="M32" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="N32" t="n">
-        <v>0.75</v>
+        <v>0.2</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R32" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="S32" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="T32" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -5355,604 +5355,604 @@
         <v>2</v>
       </c>
       <c r="Z32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AL32" t="n">
         <v>2</v>
       </c>
-      <c r="AA32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>24:08</t>
+          <t>25:50</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>4.16</v>
+        <v>7.64</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.55</v>
+        <v>0.404</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.672</v>
+        <v>0.461</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.022</v>
+        <v>0.681</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.24</v>
+        <v>0.262</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.6</v>
+        <v>0.192</v>
       </c>
       <c r="AU32" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AW32" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.147</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.068</v>
+        <v>0.037</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.111</v>
+        <v>0.074</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.008</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#20 D. HALL (Per Game)</t>
+          <t>#30 C. SILVA (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>6.5</v>
+        <v>3.6</v>
       </c>
       <c r="D33" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="E33" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T33" t="n">
+        <v>21</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="AO33" t="n">
+        <v>3.552</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.014</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AU33" t="n">
         <v>0.75</v>
       </c>
-      <c r="G33" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2</v>
-      </c>
-      <c r="K33" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2</v>
-      </c>
-      <c r="R33" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T33" t="n">
-        <v>25</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0.769</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>47:41</t>
-        </is>
-      </c>
-      <c r="AO33" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0.256</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0.238</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>1</v>
-      </c>
       <c r="AV33" t="n">
-        <v>2.625</v>
+        <v>3</v>
       </c>
       <c r="AW33" t="n">
-        <v>3.625</v>
+        <v>3.75</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.081</v>
+        <v>0.264</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.021</v>
+        <v>0.217</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.044</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.065</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#30 C. SILVA (Per Game)</t>
+          <t>#50 B. COLSON (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T34" t="n">
+        <v>13</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AO34" t="n">
+        <v>2.528</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
         <v>4</v>
-      </c>
-      <c r="C34" t="n">
-        <v>4</v>
-      </c>
-      <c r="D34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T34" t="n">
-        <v>20</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>06:20</t>
-        </is>
-      </c>
-      <c r="AO34" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0.743</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>1.163</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0.218</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>3</v>
       </c>
       <c r="AW34" t="n">
         <v>4</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.267</v>
+        <v>0.138</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.258</v>
+        <v>0.08</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.094</v>
+        <v>0.158</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#50 B. COLSON (Per Game)</t>
+          <t>#92 K. BIRCH (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C35" t="n">
-        <v>2.75</v>
+        <v>6.6</v>
       </c>
       <c r="D35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T35" t="n">
+        <v>55</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD35" t="n">
         <v>0.5</v>
       </c>
-      <c r="E35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F35" t="n">
+      <c r="AE35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="AO35" t="n">
+        <v>5.456</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="AU35" t="n">
         <v>0.25</v>
       </c>
-      <c r="G35" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H35" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1</v>
-      </c>
-      <c r="T35" t="n">
-        <v>14</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>24:58</t>
-        </is>
-      </c>
-      <c r="AO35" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>0.172</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>0</v>
-      </c>
       <c r="AV35" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.057</v>
+        <v>0.131</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.039</v>
+        <v>0.151</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.06</v>
+        <v>0.185</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#92 K. BIRCH (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -5961,82 +5961,82 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="L36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.889</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
         <v>0</v>
@@ -6058,117 +6058,117 @@
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>45:08</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.735</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.282</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.128</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>5.333</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>5.667</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.064</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.08699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.08599999999999999</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>21.8</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>39.8</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>24.6</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>14.8</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>16.6</v>
       </c>
       <c r="K37" t="n">
-        <v>2.25</v>
+        <v>23</v>
       </c>
       <c r="L37" t="n">
-        <v>1.25</v>
+        <v>11.8</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.5</v>
+        <v>11.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>19.8</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>19.8</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>468</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
@@ -6177,90 +6177,90 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>24.6</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>29.4</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>0.837</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>0.424</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>0.227</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>0.545</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>20.2</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>0.327</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>205:00</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>82.512</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>0.548</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>0.575</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>0.989</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>0.141</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>0.171</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>1.431</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>5.552</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>6.983</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="BA37" t="n">
         <v>0</v>
@@ -6269,495 +6269,165 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="D38" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="E38" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="F38" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="G38" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="H38" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I38" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="J38" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="K38" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="L38" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="M38" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N38" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>9</v>
+      </c>
+      <c r="R38" t="n">
+        <v>18</v>
+      </c>
+      <c r="S38" t="n">
+        <v>22</v>
+      </c>
+      <c r="T38" t="n">
+        <v>483</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF38" t="n">
         <v>4</v>
       </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>12</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0</v>
-      </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>0.312</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>0.316</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>205:00</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>0.5</v>
+        <v>81.736</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>0.984</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>0.291</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>1.736</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>5.698</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>7.434</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>0.198</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>0.066</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>4</v>
-      </c>
-      <c r="C39" t="n">
-        <v>86.75</v>
-      </c>
-      <c r="D39" t="n">
-        <v>24</v>
-      </c>
-      <c r="E39" t="n">
-        <v>43.25</v>
-      </c>
-      <c r="F39" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="G39" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="H39" t="n">
-        <v>11</v>
-      </c>
-      <c r="I39" t="n">
-        <v>14.75</v>
-      </c>
-      <c r="J39" t="n">
-        <v>17.25</v>
-      </c>
-      <c r="K39" t="n">
-        <v>22.25</v>
-      </c>
-      <c r="L39" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N39" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="R39" t="n">
-        <v>20.25</v>
-      </c>
-      <c r="S39" t="n">
-        <v>20</v>
-      </c>
-      <c r="T39" t="n">
-        <v>404</v>
-      </c>
-      <c r="U39" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="V39" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="W39" t="n">
-        <v>5</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>31.25</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0.848</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0.413</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0.176</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>18.25</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>206:15</t>
-        </is>
-      </c>
-      <c r="AO39" t="n">
-        <v>83.73999999999999</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>1.036</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>0.169</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>1.408</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>5.306</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>6.714</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>4</v>
-      </c>
-      <c r="C40" t="n">
-        <v>80.75</v>
-      </c>
-      <c r="D40" t="n">
-        <v>19.25</v>
-      </c>
-      <c r="E40" t="n">
-        <v>34.25</v>
-      </c>
-      <c r="F40" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="G40" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="H40" t="n">
-        <v>19</v>
-      </c>
-      <c r="I40" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="J40" t="n">
-        <v>19</v>
-      </c>
-      <c r="K40" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="L40" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="M40" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="N40" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="R40" t="n">
-        <v>18</v>
-      </c>
-      <c r="S40" t="n">
-        <v>22.25</v>
-      </c>
-      <c r="T40" t="n">
-        <v>384</v>
-      </c>
-      <c r="U40" t="n">
-        <v>10</v>
-      </c>
-      <c r="V40" t="n">
-        <v>11</v>
-      </c>
-      <c r="W40" t="n">
-        <v>9</v>
-      </c>
-      <c r="X40" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>38.75</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0.839</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>7</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>0.298</v>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>206:15</t>
-        </is>
-      </c>
-      <c r="AO40" t="n">
-        <v>82.97</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>0.508</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>0.5610000000000001</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>0.973</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>0.313</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>1.727</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>5.523</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>0.198</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="BA40" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_FENERBAHCE BEKO ISTANBUL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_FENERBAHCE BEKO ISTANBUL.xlsx
@@ -671,13 +671,13 @@
         <v>0.1708074534161491</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="M2" t="n">
         <v>56</v>
@@ -752,13 +752,13 @@
         <v>1.097560975609756</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>0.5849056603773585</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.03389830508474576</v>
+        <v>1.11864406779661</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN2" t="n">
         <v>1.431034482758621</v>
@@ -801,13 +801,13 @@
         <v>0.1708074534161491</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4</v>
+        <v>13.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="M3" t="n">
         <v>11.2</v>
@@ -882,13 +882,13 @@
         <v>1.097560975609756</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>0.5849056603773585</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.03389830508474576</v>
+        <v>1.11864406779661</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN3" t="n">
         <v>1.431034482758621</v>
@@ -931,13 +931,13 @@
         <v>0.2913907284768212</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="M4" t="n">
         <v>45</v>
@@ -1012,13 +1012,13 @@
         <v>0.9473684210526315</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>0.7413793103448276</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>0.9821428571428571</v>
       </c>
       <c r="AM4" t="n">
-        <v>2</v>
+        <v>1.814814814814815</v>
       </c>
       <c r="AN4" t="n">
         <v>1.735849056603774</v>
@@ -1061,13 +1061,13 @@
         <v>0.2913907284768212</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M5" t="n">
         <v>9</v>
@@ -1142,13 +1142,13 @@
         <v>0.9473684210526317</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>0.7413793103448276</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>0.9821428571428572</v>
       </c>
       <c r="AM5" t="n">
-        <v>2</v>
+        <v>1.814814814814815</v>
       </c>
       <c r="AN5" t="n">
         <v>1.735849056603773</v>
@@ -1486,16 +1486,16 @@
         <v>87</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="n">
         <v>8</v>
@@ -1651,16 +1651,16 @@
         <v>65</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V9" t="n">
+        <v>8</v>
+      </c>
+      <c r="W9" t="n">
         <v>2</v>
       </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
         <v>17</v>
@@ -1816,16 +1816,16 @@
         <v>71</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y10" t="n">
         <v>34</v>
@@ -2149,13 +2149,13 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="n">
         <v>7</v>
@@ -2311,10 +2311,10 @@
         <v>63</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -2644,13 +2644,13 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
         <v>8</v>
@@ -2806,10 +2806,10 @@
         <v>20</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -3139,13 +3139,13 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
         <v>4</v>
@@ -3304,13 +3304,13 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="n">
         <v>18</v>
@@ -3631,16 +3631,16 @@
         <v>468</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="V21" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y21" t="n">
         <v>123</v>
@@ -3796,16 +3796,16 @@
         <v>483</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="W22" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="Y22" t="n">
         <v>152</v>
@@ -4020,16 +4020,16 @@
         <v>87</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Y24" t="n">
         <v>1.6</v>
@@ -4185,16 +4185,16 @@
         <v>65</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W25" t="n">
         <v>0.4</v>
       </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Y25" t="n">
         <v>3.4</v>
@@ -4350,16 +4350,16 @@
         <v>71</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y26" t="n">
         <v>6.8</v>
@@ -4683,13 +4683,13 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Y28" t="n">
         <v>1.4</v>
@@ -4845,10 +4845,10 @@
         <v>63</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -5178,13 +5178,13 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Y31" t="n">
         <v>1.6</v>
@@ -5340,10 +5340,10 @@
         <v>20</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -5508,7 +5508,7 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
@@ -5673,13 +5673,13 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Y34" t="n">
         <v>0.8</v>
@@ -5838,13 +5838,13 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Y35" t="n">
         <v>3.6</v>
@@ -6165,16 +6165,16 @@
         <v>468</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="V37" t="n">
-        <v>0.4</v>
+        <v>13.2</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Y37" t="n">
         <v>24.6</v>
@@ -6330,16 +6330,16 @@
         <v>483</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W38" t="n">
-        <v>0.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X38" t="n">
-        <v>0.4</v>
+        <v>5.4</v>
       </c>
       <c r="Y38" t="n">
         <v>30.4</v>

--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_FENERBAHCE BEKO ISTANBUL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_FENERBAHCE BEKO ISTANBUL.xlsx
@@ -683,13 +683,13 @@
         <v>56</v>
       </c>
       <c r="N2" t="n">
-        <v>123</v>
+        <v>68</v>
       </c>
       <c r="O2" t="n">
-        <v>147</v>
+        <v>92</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4565217391304348</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="Q2" t="n">
         <v>36</v>
@@ -710,25 +710,25 @@
         <v>0.06832298136645963</v>
       </c>
       <c r="W2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="X2" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.06832298136645963</v>
+        <v>0.08385093167701864</v>
       </c>
       <c r="Z2" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="AA2" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3136645962732919</v>
+        <v>0.2981366459627329</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8367346938775511</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="AD2" t="n">
         <v>0.4235294117647059</v>
@@ -737,13 +737,13 @@
         <v>0.2272727272727273</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5185185185185185</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3267326732673267</v>
+        <v>0.3229166666666667</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.673469387755102</v>
+        <v>1.478260869565217</v>
       </c>
       <c r="AI2" t="n">
         <v>0.4545454545454545</v>
@@ -813,13 +813,13 @@
         <v>11.2</v>
       </c>
       <c r="N3" t="n">
-        <v>24.6</v>
+        <v>13.6</v>
       </c>
       <c r="O3" t="n">
-        <v>29.4</v>
+        <v>18.4</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4565217391304347</v>
+        <v>0.2857142857142856</v>
       </c>
       <c r="Q3" t="n">
         <v>7.2</v>
@@ -840,25 +840,25 @@
         <v>0.06832298136645963</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="X3" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.06832298136645963</v>
+        <v>0.08385093167701863</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.2</v>
+        <v>19.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3136645962732919</v>
+        <v>0.2981366459627329</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8367346938775511</v>
+        <v>0.7391304347826088</v>
       </c>
       <c r="AD3" t="n">
         <v>0.4235294117647059</v>
@@ -867,13 +867,13 @@
         <v>0.2272727272727273</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5185185185185185</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3267326732673267</v>
+        <v>0.3229166666666667</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.673469387755102</v>
+        <v>1.478260869565218</v>
       </c>
       <c r="AI3" t="n">
         <v>0.4545454545454545</v>
@@ -943,13 +943,13 @@
         <v>45</v>
       </c>
       <c r="N4" t="n">
-        <v>152</v>
+        <v>64</v>
       </c>
       <c r="O4" t="n">
-        <v>180</v>
+        <v>92</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5960264900662252</v>
+        <v>0.304635761589404</v>
       </c>
       <c r="Q4" t="n">
         <v>22</v>
@@ -970,25 +970,25 @@
         <v>0.06622516556291391</v>
       </c>
       <c r="W4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.05298013245033113</v>
+        <v>0.06291390728476821</v>
       </c>
       <c r="Z4" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="AA4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3874172185430463</v>
+        <v>0.3774834437086093</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8444444444444444</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="AD4" t="n">
         <v>0.3859649122807017</v>
@@ -997,13 +997,13 @@
         <v>0.4</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3125</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3162393162393162</v>
+        <v>0.2982456140350877</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.688888888888889</v>
+        <v>1.391304347826087</v>
       </c>
       <c r="AI4" t="n">
         <v>0.8</v>
@@ -1073,13 +1073,13 @@
         <v>9</v>
       </c>
       <c r="N5" t="n">
-        <v>30.4</v>
+        <v>12.8</v>
       </c>
       <c r="O5" t="n">
-        <v>36</v>
+        <v>18.4</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5960264900662252</v>
+        <v>0.304635761589404</v>
       </c>
       <c r="Q5" t="n">
         <v>4.4</v>
@@ -1100,25 +1100,25 @@
         <v>0.06622516556291391</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="X5" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.05298013245033113</v>
+        <v>0.06291390728476821</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>23.4</v>
+        <v>22.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3874172185430463</v>
+        <v>0.3774834437086093</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8444444444444444</v>
+        <v>0.6956521739130436</v>
       </c>
       <c r="AD5" t="n">
         <v>0.3859649122807018</v>
@@ -1127,19 +1127,19 @@
         <v>0.4</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3125</v>
+        <v>0.4210526315789474</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3162393162393163</v>
+        <v>0.2982456140350877</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.688888888888889</v>
+        <v>1.391304347826087</v>
       </c>
       <c r="AI5" t="n">
         <v>0.8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.9473684210526317</v>
+        <v>0.9473684210526316</v>
       </c>
       <c r="AK5" t="n">
         <v>0.7413793103448276</v>
@@ -1498,13 +1498,13 @@
         <v>2</v>
       </c>
       <c r="Y8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.8</v>
+        <v>0.714</v>
       </c>
       <c r="AB8" t="n">
         <v>15</v>
@@ -1663,13 +1663,13 @@
         <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Z9" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.944</v>
+        <v>0.909</v>
       </c>
       <c r="AB9" t="n">
         <v>2</v>
@@ -1690,22 +1690,22 @@
         <v>0.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AK9" t="n">
         <v>3</v>
       </c>
-      <c r="AJ9" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>4</v>
-      </c>
       <c r="AL9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.308</v>
+        <v>0.25</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
@@ -1828,13 +1828,13 @@
         <v>12</v>
       </c>
       <c r="Y10" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="Z10" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.704</v>
       </c>
       <c r="AB10" t="n">
         <v>5</v>
@@ -1858,7 +1858,7 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
@@ -1867,10 +1867,10 @@
         <v>2</v>
       </c>
       <c r="AL10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.125</v>
+        <v>0.133</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
@@ -2158,10 +2158,10 @@
         <v>3</v>
       </c>
       <c r="Y12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AA12" t="n">
         <v>1</v>
@@ -2323,13 +2323,13 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.667</v>
+        <v>0.625</v>
       </c>
       <c r="AB13" t="n">
         <v>6</v>
@@ -2350,22 +2350,22 @@
         <v>0.333</v>
       </c>
       <c r="AH13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.833</v>
+        <v>0.857</v>
       </c>
       <c r="AK13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.464</v>
+        <v>0.444</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
@@ -2653,10 +2653,10 @@
         <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Z15" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AA15" t="n">
         <v>1</v>
@@ -2818,13 +2818,13 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Z16" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.714</v>
+        <v>0.556</v>
       </c>
       <c r="AB16" t="n">
         <v>1</v>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
@@ -2857,10 +2857,10 @@
         <v>3</v>
       </c>
       <c r="AL16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
@@ -2983,13 +2983,13 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Z17" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.846</v>
+        <v>0.778</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -3148,13 +3148,13 @@
         <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>2</v>
@@ -3178,16 +3178,16 @@
         <v>1</v>
       </c>
       <c r="AI18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
         <v>0</v>
@@ -3313,13 +3313,13 @@
         <v>2</v>
       </c>
       <c r="Y19" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.857</v>
+        <v>0.786</v>
       </c>
       <c r="AB19" t="n">
         <v>1</v>
@@ -3643,13 +3643,13 @@
         <v>22</v>
       </c>
       <c r="Y21" t="n">
-        <v>123</v>
+        <v>68</v>
       </c>
       <c r="Z21" t="n">
-        <v>147</v>
+        <v>92</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.837</v>
+        <v>0.739</v>
       </c>
       <c r="AB21" t="n">
         <v>36</v>
@@ -3670,22 +3670,22 @@
         <v>0.227</v>
       </c>
       <c r="AH21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AI21" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.545</v>
+        <v>0.519</v>
       </c>
       <c r="AK21" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="AL21" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.327</v>
+        <v>0.323</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
@@ -3808,13 +3808,13 @@
         <v>27</v>
       </c>
       <c r="Y22" t="n">
-        <v>152</v>
+        <v>64</v>
       </c>
       <c r="Z22" t="n">
-        <v>180</v>
+        <v>92</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.844</v>
+        <v>0.696</v>
       </c>
       <c r="AB22" t="n">
         <v>22</v>
@@ -3835,22 +3835,22 @@
         <v>0.4</v>
       </c>
       <c r="AH22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AI22" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.312</v>
+        <v>0.421</v>
       </c>
       <c r="AK22" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="AL22" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.316</v>
+        <v>0.298</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
@@ -4032,13 +4032,13 @@
         <v>0.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.8</v>
+        <v>0.714</v>
       </c>
       <c r="AB24" t="n">
         <v>3</v>
@@ -4197,13 +4197,13 @@
         <v>0.2</v>
       </c>
       <c r="Y25" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.944</v>
+        <v>0.909</v>
       </c>
       <c r="AB25" t="n">
         <v>0.4</v>
@@ -4224,22 +4224,22 @@
         <v>0.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="AI25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AK25" t="n">
         <v>0.6</v>
       </c>
-      <c r="AJ25" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>0.8</v>
-      </c>
       <c r="AL25" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.308</v>
+        <v>0.25</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
@@ -4362,13 +4362,13 @@
         <v>2.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>6.8</v>
+        <v>3.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>8.4</v>
+        <v>5.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.704</v>
       </c>
       <c r="AB26" t="n">
         <v>1</v>
@@ -4392,7 +4392,7 @@
         <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="AJ26" t="n">
         <v>0</v>
@@ -4401,10 +4401,10 @@
         <v>0.4</v>
       </c>
       <c r="AL26" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.125</v>
+        <v>0.133</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
@@ -4692,10 +4692,10 @@
         <v>0.6</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="AA28" t="n">
         <v>1</v>
@@ -4857,13 +4857,13 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.667</v>
+        <v>0.625</v>
       </c>
       <c r="AB29" t="n">
         <v>1.2</v>
@@ -4884,22 +4884,22 @@
         <v>0.333</v>
       </c>
       <c r="AH29" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.833</v>
+        <v>0.857</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AL29" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.464</v>
+        <v>0.444</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
@@ -5187,10 +5187,10 @@
         <v>0.2</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="AA31" t="n">
         <v>1</v>
@@ -5352,13 +5352,13 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.714</v>
+        <v>0.556</v>
       </c>
       <c r="AB32" t="n">
         <v>0.2</v>
@@ -5382,7 +5382,7 @@
         <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AJ32" t="n">
         <v>0</v>
@@ -5391,10 +5391,10 @@
         <v>0.6</v>
       </c>
       <c r="AL32" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
@@ -5517,13 +5517,13 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.846</v>
+        <v>0.778</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -5682,13 +5682,13 @@
         <v>0.2</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
         <v>0.4</v>
@@ -5712,16 +5712,16 @@
         <v>0.2</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AK34" t="n">
         <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
         <v>0</v>
@@ -5847,13 +5847,13 @@
         <v>0.4</v>
       </c>
       <c r="Y35" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="Z35" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.857</v>
+        <v>0.786</v>
       </c>
       <c r="AB35" t="n">
         <v>0.2</v>
@@ -6177,13 +6177,13 @@
         <v>4.4</v>
       </c>
       <c r="Y37" t="n">
-        <v>24.6</v>
+        <v>13.6</v>
       </c>
       <c r="Z37" t="n">
-        <v>29.4</v>
+        <v>18.4</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.837</v>
+        <v>0.739</v>
       </c>
       <c r="AB37" t="n">
         <v>7.2</v>
@@ -6204,22 +6204,22 @@
         <v>0.227</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AI37" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.545</v>
+        <v>0.519</v>
       </c>
       <c r="AK37" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AL37" t="n">
-        <v>20.2</v>
+        <v>19.2</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.327</v>
+        <v>0.323</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
@@ -6342,13 +6342,13 @@
         <v>5.4</v>
       </c>
       <c r="Y38" t="n">
-        <v>30.4</v>
+        <v>12.8</v>
       </c>
       <c r="Z38" t="n">
-        <v>36</v>
+        <v>18.4</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.844</v>
+        <v>0.696</v>
       </c>
       <c r="AB38" t="n">
         <v>4.4</v>
@@ -6369,22 +6369,22 @@
         <v>0.4</v>
       </c>
       <c r="AH38" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AI38" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.312</v>
+        <v>0.421</v>
       </c>
       <c r="AK38" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AL38" t="n">
-        <v>23.4</v>
+        <v>22.8</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.316</v>
+        <v>0.298</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
